--- a/artfynd/A 36927-2026 artfynd.xlsx
+++ b/artfynd/A 36927-2026 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>136690114</v>
       </c>
       <c r="B5" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136690320</v>
       </c>
       <c r="B6" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136690937</v>
       </c>
       <c r="B7" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>136685526</v>
       </c>
       <c r="B16" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 36927-2026 artfynd.xlsx
+++ b/artfynd/A 36927-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136684751</v>
       </c>
       <c r="B2" t="n">
-        <v>89470</v>
+        <v>89472</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136690300</v>
       </c>
       <c r="B3" t="n">
-        <v>89470</v>
+        <v>89472</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136690380</v>
       </c>
       <c r="B4" t="n">
-        <v>89470</v>
+        <v>89472</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136690114</v>
       </c>
       <c r="B5" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136690320</v>
       </c>
       <c r="B6" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136690937</v>
       </c>
       <c r="B7" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136684594</v>
       </c>
       <c r="B8" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136684812</v>
       </c>
       <c r="B9" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136684916</v>
       </c>
       <c r="B10" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136685028</v>
       </c>
       <c r="B11" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136687310</v>
       </c>
       <c r="B12" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136690624</v>
       </c>
       <c r="B13" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>136686073</v>
       </c>
       <c r="B14" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>136686248</v>
       </c>
       <c r="B15" t="n">
-        <v>80590</v>
+        <v>80592</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>136685526</v>
       </c>
       <c r="B16" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>136684525</v>
       </c>
       <c r="B17" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>136684839</v>
       </c>
       <c r="B18" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136684901</v>
       </c>
       <c r="B19" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>136684997</v>
       </c>
       <c r="B20" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136685468</v>
       </c>
       <c r="B21" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>136685504</v>
       </c>
       <c r="B22" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>136685565</v>
       </c>
       <c r="B23" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136686170</v>
       </c>
       <c r="B24" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136687160</v>
       </c>
       <c r="B25" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>136685553</v>
       </c>
       <c r="B26" t="n">
-        <v>83444</v>
+        <v>83446</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>136685800</v>
       </c>
       <c r="B27" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>136686050</v>
       </c>
       <c r="B28" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>136686126</v>
       </c>
       <c r="B29" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>136686229</v>
       </c>
       <c r="B30" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>136686664</v>
       </c>
       <c r="B31" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>136686994</v>
       </c>
       <c r="B32" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>136687057</v>
       </c>
       <c r="B33" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>136690158</v>
       </c>
       <c r="B34" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>136686258</v>
       </c>
       <c r="B35" t="n">
-        <v>80594</v>
+        <v>80596</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>136686076</v>
       </c>
       <c r="B36" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>136686255</v>
       </c>
       <c r="B37" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136684790</v>
       </c>
       <c r="B38" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>136684941</v>
       </c>
       <c r="B39" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>136685541</v>
       </c>
       <c r="B40" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>136686812</v>
       </c>
       <c r="B41" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>136687070</v>
       </c>
       <c r="B42" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>136690205</v>
       </c>
       <c r="B43" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136690507</v>
       </c>
       <c r="B44" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>136690570</v>
       </c>
       <c r="B45" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>136690661</v>
       </c>
       <c r="B46" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>136690738</v>
       </c>
       <c r="B47" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>136690828</v>
       </c>
       <c r="B48" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>136690928</v>
       </c>
       <c r="B49" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>136690951</v>
       </c>
       <c r="B50" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>136690930</v>
       </c>
       <c r="B51" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 36927-2026 artfynd.xlsx
+++ b/artfynd/A 36927-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136684751</v>
       </c>
       <c r="B2" t="n">
-        <v>89472</v>
+        <v>89474</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136690300</v>
       </c>
       <c r="B3" t="n">
-        <v>89472</v>
+        <v>89474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136690380</v>
       </c>
       <c r="B4" t="n">
-        <v>89472</v>
+        <v>89474</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136690114</v>
       </c>
       <c r="B5" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136690320</v>
       </c>
       <c r="B6" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136690937</v>
       </c>
       <c r="B7" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>136685526</v>
       </c>
       <c r="B16" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 36927-2026 artfynd.xlsx
+++ b/artfynd/A 36927-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136684751</v>
       </c>
       <c r="B2" t="n">
-        <v>89474</v>
+        <v>89476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136690300</v>
       </c>
       <c r="B3" t="n">
-        <v>89474</v>
+        <v>89476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136690380</v>
       </c>
       <c r="B4" t="n">
-        <v>89474</v>
+        <v>89476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136690114</v>
       </c>
       <c r="B5" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136690320</v>
       </c>
       <c r="B6" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136690937</v>
       </c>
       <c r="B7" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136684594</v>
       </c>
       <c r="B8" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136684812</v>
       </c>
       <c r="B9" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136684916</v>
       </c>
       <c r="B10" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136685028</v>
       </c>
       <c r="B11" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136687310</v>
       </c>
       <c r="B12" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136690624</v>
       </c>
       <c r="B13" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>136686073</v>
       </c>
       <c r="B14" t="n">
-        <v>80592</v>
+        <v>80596</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>136686248</v>
       </c>
       <c r="B15" t="n">
-        <v>80592</v>
+        <v>80596</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>136685526</v>
       </c>
       <c r="B16" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>136684525</v>
       </c>
       <c r="B17" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>136684839</v>
       </c>
       <c r="B18" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136684901</v>
       </c>
       <c r="B19" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>136684997</v>
       </c>
       <c r="B20" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136685468</v>
       </c>
       <c r="B21" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>136685504</v>
       </c>
       <c r="B22" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>136685565</v>
       </c>
       <c r="B23" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136686170</v>
       </c>
       <c r="B24" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136687160</v>
       </c>
       <c r="B25" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>136685553</v>
       </c>
       <c r="B26" t="n">
-        <v>83446</v>
+        <v>83450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>136685800</v>
       </c>
       <c r="B27" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>136686050</v>
       </c>
       <c r="B28" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>136686126</v>
       </c>
       <c r="B29" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>136686229</v>
       </c>
       <c r="B30" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>136686664</v>
       </c>
       <c r="B31" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>136686994</v>
       </c>
       <c r="B32" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>136687057</v>
       </c>
       <c r="B33" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>136690158</v>
       </c>
       <c r="B34" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>136686258</v>
       </c>
       <c r="B35" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>136686076</v>
       </c>
       <c r="B36" t="n">
-        <v>80602</v>
+        <v>80606</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>136686255</v>
       </c>
       <c r="B37" t="n">
-        <v>80602</v>
+        <v>80606</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 36927-2026 artfynd.xlsx
+++ b/artfynd/A 36927-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136684751</v>
       </c>
       <c r="B2" t="n">
-        <v>89476</v>
+        <v>89478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136690300</v>
       </c>
       <c r="B3" t="n">
-        <v>89476</v>
+        <v>89478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136690380</v>
       </c>
       <c r="B4" t="n">
-        <v>89476</v>
+        <v>89478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136690114</v>
       </c>
       <c r="B5" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136690320</v>
       </c>
       <c r="B6" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136690937</v>
       </c>
       <c r="B7" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136684594</v>
       </c>
       <c r="B8" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136684812</v>
       </c>
       <c r="B9" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136684916</v>
       </c>
       <c r="B10" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136685028</v>
       </c>
       <c r="B11" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136687310</v>
       </c>
       <c r="B12" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136690624</v>
       </c>
       <c r="B13" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>136686073</v>
       </c>
       <c r="B14" t="n">
-        <v>80596</v>
+        <v>80598</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>136686248</v>
       </c>
       <c r="B15" t="n">
-        <v>80596</v>
+        <v>80598</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>136685526</v>
       </c>
       <c r="B16" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>136684525</v>
       </c>
       <c r="B17" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>136684839</v>
       </c>
       <c r="B18" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136684901</v>
       </c>
       <c r="B19" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>136684997</v>
       </c>
       <c r="B20" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136685468</v>
       </c>
       <c r="B21" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>136685504</v>
       </c>
       <c r="B22" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>136685565</v>
       </c>
       <c r="B23" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136686170</v>
       </c>
       <c r="B24" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136687160</v>
       </c>
       <c r="B25" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>136685553</v>
       </c>
       <c r="B26" t="n">
-        <v>83450</v>
+        <v>83452</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>136685800</v>
       </c>
       <c r="B27" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>136686050</v>
       </c>
       <c r="B28" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>136686126</v>
       </c>
       <c r="B29" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>136686229</v>
       </c>
       <c r="B30" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>136686664</v>
       </c>
       <c r="B31" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>136686994</v>
       </c>
       <c r="B32" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>136687057</v>
       </c>
       <c r="B33" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>136690158</v>
       </c>
       <c r="B34" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>136686258</v>
       </c>
       <c r="B35" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>136686076</v>
       </c>
       <c r="B36" t="n">
-        <v>80606</v>
+        <v>80608</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>136686255</v>
       </c>
       <c r="B37" t="n">
-        <v>80606</v>
+        <v>80608</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 36927-2026 artfynd.xlsx
+++ b/artfynd/A 36927-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136684751</v>
       </c>
       <c r="B2" t="n">
-        <v>89478</v>
+        <v>89479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136690300</v>
       </c>
       <c r="B3" t="n">
-        <v>89478</v>
+        <v>89479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136690380</v>
       </c>
       <c r="B4" t="n">
-        <v>89478</v>
+        <v>89479</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136690114</v>
       </c>
       <c r="B5" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136690320</v>
       </c>
       <c r="B6" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136690937</v>
       </c>
       <c r="B7" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136684594</v>
       </c>
       <c r="B8" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136684812</v>
       </c>
       <c r="B9" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136684916</v>
       </c>
       <c r="B10" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136685028</v>
       </c>
       <c r="B11" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136687310</v>
       </c>
       <c r="B12" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136690624</v>
       </c>
       <c r="B13" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>136686073</v>
       </c>
       <c r="B14" t="n">
-        <v>80598</v>
+        <v>80599</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>136686248</v>
       </c>
       <c r="B15" t="n">
-        <v>80598</v>
+        <v>80599</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>136685526</v>
       </c>
       <c r="B16" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>136684525</v>
       </c>
       <c r="B17" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>136684839</v>
       </c>
       <c r="B18" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136684901</v>
       </c>
       <c r="B19" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>136684997</v>
       </c>
       <c r="B20" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136685468</v>
       </c>
       <c r="B21" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>136685504</v>
       </c>
       <c r="B22" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>136685565</v>
       </c>
       <c r="B23" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136686170</v>
       </c>
       <c r="B24" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136687160</v>
       </c>
       <c r="B25" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>136685553</v>
       </c>
       <c r="B26" t="n">
-        <v>83452</v>
+        <v>83453</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>136685800</v>
       </c>
       <c r="B27" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>136686050</v>
       </c>
       <c r="B28" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>136686126</v>
       </c>
       <c r="B29" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>136686229</v>
       </c>
       <c r="B30" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>136686664</v>
       </c>
       <c r="B31" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>136686994</v>
       </c>
       <c r="B32" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>136687057</v>
       </c>
       <c r="B33" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>136690158</v>
       </c>
       <c r="B34" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>136686258</v>
       </c>
       <c r="B35" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>136686076</v>
       </c>
       <c r="B36" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>136686255</v>
       </c>
       <c r="B37" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 36927-2026 artfynd.xlsx
+++ b/artfynd/A 36927-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136684751</v>
       </c>
       <c r="B2" t="n">
-        <v>89479</v>
+        <v>89485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136690300</v>
       </c>
       <c r="B3" t="n">
-        <v>89479</v>
+        <v>89485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136690380</v>
       </c>
       <c r="B4" t="n">
-        <v>89479</v>
+        <v>89485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136690114</v>
       </c>
       <c r="B5" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136690320</v>
       </c>
       <c r="B6" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136690937</v>
       </c>
       <c r="B7" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>136685526</v>
       </c>
       <c r="B16" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 36927-2026 artfynd.xlsx
+++ b/artfynd/A 36927-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136684751</v>
       </c>
       <c r="B2" t="n">
-        <v>89485</v>
+        <v>89489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136690300</v>
       </c>
       <c r="B3" t="n">
-        <v>89485</v>
+        <v>89489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136690380</v>
       </c>
       <c r="B4" t="n">
-        <v>89485</v>
+        <v>89489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136690114</v>
       </c>
       <c r="B5" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136690320</v>
       </c>
       <c r="B6" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136690937</v>
       </c>
       <c r="B7" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136684594</v>
       </c>
       <c r="B8" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136684812</v>
       </c>
       <c r="B9" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136684916</v>
       </c>
       <c r="B10" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136685028</v>
       </c>
       <c r="B11" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136687310</v>
       </c>
       <c r="B12" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136690624</v>
       </c>
       <c r="B13" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>136686073</v>
       </c>
       <c r="B14" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>136686248</v>
       </c>
       <c r="B15" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>136685526</v>
       </c>
       <c r="B16" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>136684525</v>
       </c>
       <c r="B17" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>136684839</v>
       </c>
       <c r="B18" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136684901</v>
       </c>
       <c r="B19" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>136684997</v>
       </c>
       <c r="B20" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136685468</v>
       </c>
       <c r="B21" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>136685504</v>
       </c>
       <c r="B22" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>136685565</v>
       </c>
       <c r="B23" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136686170</v>
       </c>
       <c r="B24" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136687160</v>
       </c>
       <c r="B25" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>136685553</v>
       </c>
       <c r="B26" t="n">
-        <v>83453</v>
+        <v>83457</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>136685800</v>
       </c>
       <c r="B27" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>136686050</v>
       </c>
       <c r="B28" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>136686126</v>
       </c>
       <c r="B29" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>136686229</v>
       </c>
       <c r="B30" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>136686664</v>
       </c>
       <c r="B31" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>136686994</v>
       </c>
       <c r="B32" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>136687057</v>
       </c>
       <c r="B33" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>136690158</v>
       </c>
       <c r="B34" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>136686258</v>
       </c>
       <c r="B35" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>136686076</v>
       </c>
       <c r="B36" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>136686255</v>
       </c>
       <c r="B37" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 36927-2026 artfynd.xlsx
+++ b/artfynd/A 36927-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136684751</v>
       </c>
       <c r="B2" t="n">
-        <v>89489</v>
+        <v>89491</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136690300</v>
       </c>
       <c r="B3" t="n">
-        <v>89489</v>
+        <v>89491</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136690380</v>
       </c>
       <c r="B4" t="n">
-        <v>89489</v>
+        <v>89491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136690114</v>
       </c>
       <c r="B5" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136690320</v>
       </c>
       <c r="B6" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136690937</v>
       </c>
       <c r="B7" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136684594</v>
       </c>
       <c r="B8" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136684812</v>
       </c>
       <c r="B9" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136684916</v>
       </c>
       <c r="B10" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136685028</v>
       </c>
       <c r="B11" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136687310</v>
       </c>
       <c r="B12" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136690624</v>
       </c>
       <c r="B13" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>136686073</v>
       </c>
       <c r="B14" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>136686248</v>
       </c>
       <c r="B15" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>136685526</v>
       </c>
       <c r="B16" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>136684525</v>
       </c>
       <c r="B17" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>136684839</v>
       </c>
       <c r="B18" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136684901</v>
       </c>
       <c r="B19" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>136684997</v>
       </c>
       <c r="B20" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136685468</v>
       </c>
       <c r="B21" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>136685504</v>
       </c>
       <c r="B22" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>136685565</v>
       </c>
       <c r="B23" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136686170</v>
       </c>
       <c r="B24" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136687160</v>
       </c>
       <c r="B25" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>136685553</v>
       </c>
       <c r="B26" t="n">
-        <v>83457</v>
+        <v>83459</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>136685800</v>
       </c>
       <c r="B27" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>136686050</v>
       </c>
       <c r="B28" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>136686126</v>
       </c>
       <c r="B29" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>136686229</v>
       </c>
       <c r="B30" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>136686664</v>
       </c>
       <c r="B31" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>136686994</v>
       </c>
       <c r="B32" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>136687057</v>
       </c>
       <c r="B33" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>136690158</v>
       </c>
       <c r="B34" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>136686258</v>
       </c>
       <c r="B35" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>136686076</v>
       </c>
       <c r="B36" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>136686255</v>
       </c>
       <c r="B37" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 36927-2026 artfynd.xlsx
+++ b/artfynd/A 36927-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136684751</v>
       </c>
       <c r="B2" t="n">
-        <v>89491</v>
+        <v>89504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136690300</v>
       </c>
       <c r="B3" t="n">
-        <v>89491</v>
+        <v>89504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136690380</v>
       </c>
       <c r="B4" t="n">
-        <v>89491</v>
+        <v>89504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136690114</v>
       </c>
       <c r="B5" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136690320</v>
       </c>
       <c r="B6" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136690937</v>
       </c>
       <c r="B7" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136684594</v>
       </c>
       <c r="B8" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136684812</v>
       </c>
       <c r="B9" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136684916</v>
       </c>
       <c r="B10" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136685028</v>
       </c>
       <c r="B11" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136687310</v>
       </c>
       <c r="B12" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136690624</v>
       </c>
       <c r="B13" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>136686073</v>
       </c>
       <c r="B14" t="n">
-        <v>80604</v>
+        <v>80617</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>136686248</v>
       </c>
       <c r="B15" t="n">
-        <v>80604</v>
+        <v>80617</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>136685526</v>
       </c>
       <c r="B16" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>136684525</v>
       </c>
       <c r="B17" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>136684839</v>
       </c>
       <c r="B18" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136684901</v>
       </c>
       <c r="B19" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>136684997</v>
       </c>
       <c r="B20" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136685468</v>
       </c>
       <c r="B21" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>136685504</v>
       </c>
       <c r="B22" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>136685565</v>
       </c>
       <c r="B23" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136686170</v>
       </c>
       <c r="B24" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136687160</v>
       </c>
       <c r="B25" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>136685553</v>
       </c>
       <c r="B26" t="n">
-        <v>83459</v>
+        <v>83472</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>136685800</v>
       </c>
       <c r="B27" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>136686050</v>
       </c>
       <c r="B28" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>136686126</v>
       </c>
       <c r="B29" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>136686229</v>
       </c>
       <c r="B30" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>136686664</v>
       </c>
       <c r="B31" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>136686994</v>
       </c>
       <c r="B32" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>136687057</v>
       </c>
       <c r="B33" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>136690158</v>
       </c>
       <c r="B34" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>136686258</v>
       </c>
       <c r="B35" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>136686076</v>
       </c>
       <c r="B36" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>136686255</v>
       </c>
       <c r="B37" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136684790</v>
       </c>
       <c r="B38" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>136684941</v>
       </c>
       <c r="B39" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>136685541</v>
       </c>
       <c r="B40" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>136686812</v>
       </c>
       <c r="B41" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>136687070</v>
       </c>
       <c r="B42" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>136690205</v>
       </c>
       <c r="B43" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136690507</v>
       </c>
       <c r="B44" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>136690570</v>
       </c>
       <c r="B45" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>136690661</v>
       </c>
       <c r="B46" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>136690738</v>
       </c>
       <c r="B47" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>136690828</v>
       </c>
       <c r="B48" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>136690928</v>
       </c>
       <c r="B49" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>136690951</v>
       </c>
       <c r="B50" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>136690930</v>
       </c>
       <c r="B51" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 36927-2026 artfynd.xlsx
+++ b/artfynd/A 36927-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136684751</v>
       </c>
       <c r="B2" t="n">
-        <v>89504</v>
+        <v>89506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136690300</v>
       </c>
       <c r="B3" t="n">
-        <v>89504</v>
+        <v>89506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136690380</v>
       </c>
       <c r="B4" t="n">
-        <v>89504</v>
+        <v>89506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136690114</v>
       </c>
       <c r="B5" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136690320</v>
       </c>
       <c r="B6" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136690937</v>
       </c>
       <c r="B7" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>136684594</v>
       </c>
       <c r="B8" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>136684812</v>
       </c>
       <c r="B9" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>136684916</v>
       </c>
       <c r="B10" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>136685028</v>
       </c>
       <c r="B11" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136687310</v>
       </c>
       <c r="B12" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>136690624</v>
       </c>
       <c r="B13" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>136686073</v>
       </c>
       <c r="B14" t="n">
-        <v>80617</v>
+        <v>80619</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>136686248</v>
       </c>
       <c r="B15" t="n">
-        <v>80617</v>
+        <v>80619</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>136685526</v>
       </c>
       <c r="B16" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>136684525</v>
       </c>
       <c r="B17" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
         <v>136684839</v>
       </c>
       <c r="B18" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136684901</v>
       </c>
       <c r="B19" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>136684997</v>
       </c>
       <c r="B20" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136685468</v>
       </c>
       <c r="B21" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>136685504</v>
       </c>
       <c r="B22" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>136685565</v>
       </c>
       <c r="B23" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>136686170</v>
       </c>
       <c r="B24" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>136687160</v>
       </c>
       <c r="B25" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>136685553</v>
       </c>
       <c r="B26" t="n">
-        <v>83472</v>
+        <v>83474</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>136685800</v>
       </c>
       <c r="B27" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>136686050</v>
       </c>
       <c r="B28" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>136686126</v>
       </c>
       <c r="B29" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>136686229</v>
       </c>
       <c r="B30" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>136686664</v>
       </c>
       <c r="B31" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>136686994</v>
       </c>
       <c r="B32" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>136687057</v>
       </c>
       <c r="B33" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>136690158</v>
       </c>
       <c r="B34" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>136686258</v>
       </c>
       <c r="B35" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>136686076</v>
       </c>
       <c r="B36" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>136686255</v>
       </c>
       <c r="B37" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>136684790</v>
       </c>
       <c r="B38" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>136684941</v>
       </c>
       <c r="B39" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>136685541</v>
       </c>
       <c r="B40" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>136686812</v>
       </c>
       <c r="B41" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>136687070</v>
       </c>
       <c r="B42" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>136690205</v>
       </c>
       <c r="B43" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>136690507</v>
       </c>
       <c r="B44" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>136690570</v>
       </c>
       <c r="B45" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>136690661</v>
       </c>
       <c r="B46" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>136690738</v>
       </c>
       <c r="B47" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>136690828</v>
       </c>
       <c r="B48" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>136690928</v>
       </c>
       <c r="B49" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>136690951</v>
       </c>
       <c r="B50" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>136690930</v>
       </c>
       <c r="B51" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 36927-2026 artfynd.xlsx
+++ b/artfynd/A 36927-2026 artfynd.xlsx
@@ -2834,11 +2834,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3409,11 +3405,7 @@
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -4765,11 +4757,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4880,11 +4868,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4995,11 +4979,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5110,11 +5090,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5225,11 +5201,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5340,11 +5312,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5455,11 +5423,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5570,11 +5534,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5685,11 +5645,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5800,11 +5756,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5915,11 +5867,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6030,11 +5978,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6145,11 +6089,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>

--- a/artfynd/A 36927-2026 artfynd.xlsx
+++ b/artfynd/A 36927-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136684751</v>
       </c>
       <c r="B2" t="n">
-        <v>89506</v>
+        <v>89509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136690300</v>
       </c>
       <c r="B3" t="n">
-        <v>89506</v>
+        <v>89509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136690380</v>
       </c>
       <c r="B4" t="n">
-        <v>89506</v>
+        <v>89509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136690114</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136690320</v>
       </c>
       <c r="B6" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>136690937</v>
       </c>
       <c r="B7" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>136685526</v>
       </c>
       <c r="B16" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>136685553</v>
       </c>
       <c r="B26" t="n">
-        <v>83474</v>
+        <v>83477</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
